--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,27 +1097,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129524403</v>
+        <v>135282890</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480983</v>
+        <v>480999</v>
       </c>
       <c r="R6" t="n">
-        <v>6596379</v>
+        <v>6596287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,27 +1176,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringbarkning i gammal tall.</t>
+          <t>Revirhävdande.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122334860</v>
+        <v>135282908</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>57624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,42 +1234,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100063</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480948</v>
+        <v>480800</v>
       </c>
       <c r="R7" t="n">
-        <v>6596353</v>
+        <v>6596438</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1302,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,46 +1326,45 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123985947</v>
+        <v>129524403</v>
       </c>
       <c r="B8" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1356,7 +1374,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1364,14 +1382,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1380,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480975</v>
+        <v>480983</v>
       </c>
       <c r="R8" t="n">
-        <v>6596293</v>
+        <v>6596379</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,22 +1423,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringbarkning i gammal tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62161683</v>
+        <v>122334860</v>
       </c>
       <c r="B9" t="n">
-        <v>96601</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,37 +1481,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster om Lillsjön, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481080</v>
+        <v>480948</v>
       </c>
       <c r="R9" t="n">
-        <v>6596477</v>
+        <v>6596353</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1517,12 +1540,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,73 +1554,83 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62161682</v>
+        <v>123985947</v>
       </c>
       <c r="B10" t="n">
-        <v>92841</v>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4745</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster om Lillsjön, Vstm</t>
+          <t>Lördagsbäcken, Lördagsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481083</v>
+        <v>480975</v>
       </c>
       <c r="R10" t="n">
-        <v>6596515</v>
+        <v>6596293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,12 +1657,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,31 +1683,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130799024</v>
+        <v>135282907</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,40 +1710,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481053</v>
+        <v>480752</v>
       </c>
       <c r="R11" t="n">
-        <v>6596545</v>
+        <v>6596395</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,12 +1778,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,29 +1807,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130798963</v>
+        <v>135282910</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>98623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,57 +1836,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220007</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Missne</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calla palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481221</v>
+        <v>480769</v>
       </c>
       <c r="R12" t="n">
-        <v>6596393</v>
+        <v>6596482</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,17 +1890,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130799006</v>
+        <v>62161683</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>96601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,53 +1943,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Väster om Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481205</v>
+        <v>481080</v>
       </c>
       <c r="R13" t="n">
-        <v>6596516</v>
+        <v>6596477</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,12 +1997,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,68 +2013,74 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134433704</v>
+        <v>62161682</v>
       </c>
       <c r="B14" t="n">
-        <v>98066</v>
+        <v>92841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Väster om Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481132</v>
+        <v>481083</v>
       </c>
       <c r="R14" t="n">
-        <v>6596362</v>
+        <v>6596515</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,27 +2104,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,65 +2120,69 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134433711</v>
+        <v>130799024</v>
       </c>
       <c r="B15" t="n">
-        <v>98063</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481132</v>
+        <v>481053</v>
       </c>
       <c r="R15" t="n">
-        <v>6596358</v>
+        <v>6596545</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2182,27 +2209,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,28 +2223,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134433712</v>
+        <v>130798963</v>
       </c>
       <c r="B16" t="n">
-        <v>98063</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,21 +2253,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2262,16 +2275,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481131</v>
+        <v>481221</v>
       </c>
       <c r="R16" t="n">
-        <v>6596311</v>
+        <v>6596393</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2298,27 +2327,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,15 +2352,604 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130799006</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>481205</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6596516</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135282888</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lördagsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>481041</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6596343</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134433704</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>481132</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6596362</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134433711</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>481132</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6596358</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134433712</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>481131</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6596311</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>62161683</v>
+        <v>135374602</v>
       </c>
       <c r="B13" t="n">
-        <v>96601</v>
+        <v>98060</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,34 +1943,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster om Lillsjön, Vstm</t>
+          <t>Lördagsbäcken, Lördagsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481080</v>
+        <v>480904</v>
       </c>
       <c r="R13" t="n">
-        <v>6596477</v>
+        <v>6596426</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,12 +1997,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,58 +2023,48 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>62161682</v>
+        <v>62161683</v>
       </c>
       <c r="B14" t="n">
-        <v>92841</v>
+        <v>96601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481083</v>
+        <v>481080</v>
       </c>
       <c r="R14" t="n">
-        <v>6596515</v>
+        <v>6596477</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,6 +2124,11 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2141,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130799024</v>
+        <v>62161682</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>92841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,40 +2157,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Väster om Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481053</v>
+        <v>481083</v>
       </c>
       <c r="R15" t="n">
-        <v>6596545</v>
+        <v>6596515</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,12 +2211,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,84 +2225,71 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130798963</v>
+        <v>130799024</v>
       </c>
       <c r="B16" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481221</v>
+        <v>481053</v>
       </c>
       <c r="R16" t="n">
-        <v>6596393</v>
+        <v>6596545</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2335,17 +2324,13 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2364,7 +2349,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130799006</v>
+        <v>130798963</v>
       </c>
       <c r="B17" t="n">
         <v>57141</v>
@@ -2397,11 +2382,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2415,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481205</v>
+        <v>481221</v>
       </c>
       <c r="R17" t="n">
-        <v>6596516</v>
+        <v>6596393</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2451,6 +2440,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,32 +2471,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135282888</v>
+        <v>130799006</v>
       </c>
       <c r="B18" t="n">
-        <v>58136</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2510,31 +2504,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lördagsbäcken, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481041</v>
+        <v>481205</v>
       </c>
       <c r="R18" t="n">
-        <v>6596343</v>
+        <v>6596516</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2558,27 +2552,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>04:43</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>04:43</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,44 +2572,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134433704</v>
+        <v>135282888</v>
       </c>
       <c r="B19" t="n">
-        <v>98066</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2638,19 +2617,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lördagsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481132</v>
+        <v>481041</v>
       </c>
       <c r="R19" t="n">
-        <v>6596362</v>
+        <v>6596343</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2674,27 +2665,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>04:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>04:43</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,22 +2700,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134433711</v>
+        <v>134433704</v>
       </c>
       <c r="B20" t="n">
-        <v>98063</v>
+        <v>98066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,16 +2723,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2763,7 +2754,7 @@
         <v>481132</v>
       </c>
       <c r="R20" t="n">
-        <v>6596358</v>
+        <v>6596362</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2795,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2837,7 +2828,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134433712</v>
+        <v>134433711</v>
       </c>
       <c r="B21" t="n">
         <v>98063</v>
@@ -2876,10 +2867,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481131</v>
+        <v>481132</v>
       </c>
       <c r="R21" t="n">
-        <v>6596311</v>
+        <v>6596358</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2911,7 +2902,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2912,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2950,6 +2941,122 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134433712</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>481131</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6596311</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,10 +2712,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134433704</v>
+        <v>135506024</v>
       </c>
       <c r="B20" t="n">
-        <v>98066</v>
+        <v>106199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,41 +2723,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>221154</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, SSO om, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481132</v>
+        <v>481186</v>
       </c>
       <c r="R20" t="n">
-        <v>6596362</v>
+        <v>6596385</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2781,27 +2777,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,26 +2793,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134433711</v>
+        <v>134433704</v>
       </c>
       <c r="B21" t="n">
-        <v>98063</v>
+        <v>98066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,16 +2825,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2870,7 +2856,7 @@
         <v>481132</v>
       </c>
       <c r="R21" t="n">
-        <v>6596358</v>
+        <v>6596362</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2902,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2944,7 +2930,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134433712</v>
+        <v>134433711</v>
       </c>
       <c r="B22" t="n">
         <v>98063</v>
@@ -2983,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481131</v>
+        <v>481132</v>
       </c>
       <c r="R22" t="n">
-        <v>6596311</v>
+        <v>6596358</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3018,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3028,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3057,6 +3043,220 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134433712</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>481131</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6596311</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135506027</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98064</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lillsjön, SSO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>481186</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6596385</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128332631</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122334849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134004522</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134004641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282890</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1341,6 +1371,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524403</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122334860</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1696,6 +1741,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123985947</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282907</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1929,6 +1984,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282910</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2036,6 +2096,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135374602</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2143,6 +2208,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62161683</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2245,6 +2315,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62161682</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2346,6 +2421,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799024</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2468,6 +2548,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130798963</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2581,6 +2666,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799006</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2709,6 +2799,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282888</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2811,6 +2906,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506024</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2927,6 +3027,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433704</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3043,6 +3148,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433711</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3159,6 +3269,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433712</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3257,8 +3372,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -1125,7 +1125,7 @@
         <v>135282890</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>135282908</v>
       </c>
       <c r="B7" t="n">
-        <v>57624</v>
+        <v>57629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>135282907</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>135282910</v>
       </c>
       <c r="B12" t="n">
-        <v>98623</v>
+        <v>98670</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135374602</v>
       </c>
       <c r="B13" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>135282888</v>
       </c>
       <c r="B19" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135506024</v>
       </c>
       <c r="B20" t="n">
-        <v>106199</v>
+        <v>106254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>135506027</v>
       </c>
       <c r="B24" t="n">
-        <v>98064</v>
+        <v>98108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -1883,7 +1883,7 @@
         <v>135282910</v>
       </c>
       <c r="B12" t="n">
-        <v>98670</v>
+        <v>98697</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135374602</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135506024</v>
       </c>
       <c r="B20" t="n">
-        <v>106254</v>
+        <v>106281</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>135506027</v>
       </c>
       <c r="B24" t="n">
-        <v>98108</v>
+        <v>98135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1122,27 +1122,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129524403</v>
+        <v>135282890</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480983</v>
+        <v>480999</v>
       </c>
       <c r="R6" t="n">
-        <v>6596379</v>
+        <v>6596287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,27 +1201,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringbarkning i gammal tall.</t>
+          <t>Revirhävdande.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,16 +1247,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524403</t>
+          <t>https://artportalen.se/Sighting/135282890</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122334860</v>
+        <v>135282908</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>57629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,42 +1264,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100063</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480948</v>
+        <v>480800</v>
       </c>
       <c r="R7" t="n">
-        <v>6596353</v>
+        <v>6596438</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,12 +1332,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,51 +1356,50 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122334860</t>
+          <t>https://artportalen.se/Sighting/135282908</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123985947</v>
+        <v>129524403</v>
       </c>
       <c r="B8" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1391,7 +1409,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1399,14 +1417,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1415,10 +1428,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480975</v>
+        <v>480983</v>
       </c>
       <c r="R8" t="n">
-        <v>6596293</v>
+        <v>6596379</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,22 +1458,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringbarkning i gammal tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,16 +1504,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123985947</t>
+          <t>https://artportalen.se/Sighting/129524403</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62161683</v>
+        <v>122334860</v>
       </c>
       <c r="B9" t="n">
-        <v>96601</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,37 +1521,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster om Lillsjön, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481080</v>
+        <v>480948</v>
       </c>
       <c r="R9" t="n">
-        <v>6596477</v>
+        <v>6596353</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,12 +1580,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,78 +1594,88 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62161683</t>
+          <t>https://artportalen.se/Sighting/122334860</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62161682</v>
+        <v>123985947</v>
       </c>
       <c r="B10" t="n">
-        <v>92841</v>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4745</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väster om Lillsjön, Vstm</t>
+          <t>Lördagsbäcken, Lördagsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481083</v>
+        <v>480975</v>
       </c>
       <c r="R10" t="n">
-        <v>6596515</v>
+        <v>6596293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,12 +1702,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-10-18</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,36 +1728,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62161682</t>
+          <t>https://artportalen.se/Sighting/123985947</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130799024</v>
+        <v>135282907</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,40 +1760,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481053</v>
+        <v>480752</v>
       </c>
       <c r="R11" t="n">
-        <v>6596545</v>
+        <v>6596395</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,12 +1828,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,34 +1857,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130799024</t>
+          <t>https://artportalen.se/Sighting/135282907</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130798963</v>
+        <v>135282910</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>98702</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,57 +1891,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220007</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Missne</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calla palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Stora Bergtjärn, Stora Bergtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481221</v>
+        <v>480769</v>
       </c>
       <c r="R12" t="n">
-        <v>6596393</v>
+        <v>6596482</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,17 +1945,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,27 +1975,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130798963</t>
+          <t>https://artportalen.se/Sighting/135282910</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130799006</v>
+        <v>135374602</v>
       </c>
       <c r="B13" t="n">
-        <v>57141</v>
+        <v>98136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,53 +2003,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Lördagsbäcken, Lördagsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481205</v>
+        <v>480904</v>
       </c>
       <c r="R13" t="n">
-        <v>6596516</v>
+        <v>6596426</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,12 +2057,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,27 +2087,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130799006</t>
+          <t>https://artportalen.se/Sighting/135374602</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134433704</v>
+        <v>62161683</v>
       </c>
       <c r="B14" t="n">
-        <v>98066</v>
+        <v>96601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,41 +2115,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Väster om Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481132</v>
+        <v>481080</v>
       </c>
       <c r="R14" t="n">
-        <v>6596362</v>
+        <v>6596477</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,27 +2169,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,73 +2185,79 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433704</t>
+          <t>https://artportalen.se/Sighting/62161683</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134433711</v>
+        <v>62161682</v>
       </c>
       <c r="B15" t="n">
-        <v>98063</v>
+        <v>92841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Väster om Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481132</v>
+        <v>481083</v>
       </c>
       <c r="R15" t="n">
-        <v>6596358</v>
+        <v>6596515</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2252,27 +2281,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,70 +2297,74 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433711</t>
+          <t>https://artportalen.se/Sighting/62161682</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134433712</v>
+        <v>130799024</v>
       </c>
       <c r="B16" t="n">
-        <v>98063</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481131</v>
+        <v>481053</v>
       </c>
       <c r="R16" t="n">
-        <v>6596311</v>
+        <v>6596545</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2373,27 +2391,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,24 +2405,976 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/130799024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130798963</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>481221</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6596393</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130798963</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130799006</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>481205</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6596516</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130799006</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135282888</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lördagsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>481041</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6596343</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282888</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135506024</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106286</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillsjön, SSO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>481186</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6596385</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134433704</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>481132</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6596362</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433704</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134433711</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>481132</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6596358</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433711</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134433712</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>481131</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6596311</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134433712</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135506027</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98140</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lillsjön, SSO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>481186</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6596385</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506027</t>
         </is>
       </c>
     </row>
@@ -2440,6 +3395,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -1883,7 +1883,7 @@
         <v>135282910</v>
       </c>
       <c r="B12" t="n">
-        <v>98702</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135374602</v>
       </c>
       <c r="B13" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135506024</v>
       </c>
       <c r="B20" t="n">
-        <v>106286</v>
+        <v>106288</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>135506027</v>
       </c>
       <c r="B24" t="n">
-        <v>98140</v>
+        <v>98142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -1125,7 +1125,7 @@
         <v>135282890</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>135282908</v>
       </c>
       <c r="B7" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>135282907</v>
       </c>
       <c r="B11" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>135282888</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135506024</v>
       </c>
       <c r="B20" t="n">
-        <v>106288</v>
+        <v>106308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>135506027</v>
       </c>
       <c r="B24" t="n">
-        <v>98142</v>
+        <v>98159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29739-2026 artfynd.xlsx
+++ b/artfynd/A 29739-2026 artfynd.xlsx
@@ -2810,7 +2810,7 @@
         <v>135506024</v>
       </c>
       <c r="B20" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>135506027</v>
       </c>
       <c r="B24" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
